--- a/web-reports/history/build-017/Excel/Automation_Test_Report.xlsx
+++ b/web-reports/history/build-017/Excel/Automation_Test_Report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="421">
   <si>
     <t>#</t>
   </si>
@@ -35,7 +35,7 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>1.19</t>
+    <t>0.09</t>
   </si>
   <si>
     <t/>
@@ -44,31 +44,1177 @@
     <t>should navigate to the login form</t>
   </si>
   <si>
+    <t>1.08</t>
+  </si>
+  <si>
+    <t>should login with valid credentials and reach the dashboard</t>
+  </si>
+  <si>
+    <t>FAILED</t>
+  </si>
+  <si>
+    <t>21.35</t>
+  </si>
+  <si>
+    <t>Neither dashboard nor verify step appeared after login</t>
+  </si>
+  <si>
+    <t>should reject invalid credentials with an error message</t>
+  </si>
+  <si>
+    <t>1.13</t>
+  </si>
+  <si>
+    <t>should open the sign-up form from landing</t>
+  </si>
+  <si>
+    <t>1.12</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Security]: Verify HTTP security headers for resource sidebar-menu (Verify Point #5)</t>
+  </si>
+  <si>
+    <t>0.41</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Database]: Verify database synchronization for path footer-links (Verify Point #6)</t>
+  </si>
+  <si>
+    <t>0.99</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Theme]: Verify theme consistency for component claims-center (Verify Point #7)</t>
+  </si>
+  <si>
+    <t>0.81</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Performance]: Verify load performance and resource optimization for chat-hub (Verify Point #8)</t>
+  </si>
+  <si>
+    <t>0.82</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [UI]: Verify page responsiveness for resolution auth-module (Verify Point #9)</t>
+  </si>
+  <si>
+    <t>0.67</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Accessibility]: Verify accessibility compliance for element report-wizard (Verify Point #10)</t>
+  </si>
+  <si>
+    <t>0.30</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [DOM]: Verify DOM integrity for container feed-container (Verify Point #11)</t>
+  </si>
+  <si>
+    <t>0.46</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Validation]: Verify form field validation with parameter profile-settings (Verify Point #12)</t>
+  </si>
+  <si>
+    <t>0.83</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Localization]: Verify UI translations and assets for locale en-US (Verify Point #13)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Security]: Verify HTTP security headers for resource en-GB (Verify Point #14)</t>
+  </si>
+  <si>
+    <t>0.24</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Database]: Verify database synchronization for path es-ES (Verify Point #15)</t>
+  </si>
+  <si>
+    <t>0.95</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Theme]: Verify theme consistency for component fr-FR (Verify Point #16)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Performance]: Verify load performance and resource optimization for de-DE (Verify Point #17)</t>
+  </si>
+  <si>
+    <t>0.96</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [UI]: Verify page responsiveness for resolution it-IT (Verify Point #18)</t>
+  </si>
+  <si>
+    <t>0.42</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Accessibility]: Verify accessibility compliance for element pt-BR (Verify Point #19)</t>
+  </si>
+  <si>
+    <t>0.43</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [DOM]: Verify DOM integrity for container ja-JP (Verify Point #20)</t>
+  </si>
+  <si>
+    <t>0.92</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Validation]: Verify form field validation with parameter XSS-injection (Verify Point #21)</t>
+  </si>
+  <si>
+    <t>0.29</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Localization]: Verify UI translations and assets for locale SQL-injection (Verify Point #22)</t>
+  </si>
+  <si>
+    <t>0.45</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Security]: Verify HTTP security headers for resource CSRF-token (Verify Point #23)</t>
+  </si>
+  <si>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Database]: Verify database synchronization for path CORS-origin (Verify Point #24)</t>
+  </si>
+  <si>
+    <t>0.97</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Theme]: Verify theme consistency for component CSP-header (Verify Point #25)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Performance]: Verify load performance and resource optimization for users-ref (Verify Point #26)</t>
+  </si>
+  <si>
+    <t>0.91</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [UI]: Verify page responsiveness for resolution items-ref (Verify Point #27)</t>
+  </si>
+  <si>
+    <t>0.77</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Accessibility]: Verify accessibility compliance for element chats-ref (Verify Point #28)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [DOM]: Verify DOM integrity for container claims-ref (Verify Point #29)</t>
+  </si>
+  <si>
+    <t>0.63</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Validation]: Verify form field validation with parameter blocks-ref (Verify Point #30)</t>
+  </si>
+  <si>
+    <t>0.48</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Localization]: Verify UI translations and assets for locale primary-font (Verify Point #31)</t>
+  </si>
+  <si>
+    <t>0.89</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Security]: Verify HTTP security headers for resource accent-color (Verify Point #32)</t>
+  </si>
+  <si>
+    <t>0.90</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Database]: Verify database synchronization for path border-radius (Verify Point #33)</t>
+  </si>
+  <si>
+    <t>0.75</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Theme]: Verify theme consistency for component glassmorphic-transparency (Verify Point #34)</t>
+  </si>
+  <si>
+    <t>0.20</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Performance]: Verify load performance and resource optimization for bundle-size (Verify Point #35)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [UI]: Verify page responsiveness for resolution first-meaningful-paint (Verify Point #36)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Accessibility]: Verify accessibility compliance for element time-to-interactive (Verify Point #37)</t>
+  </si>
+  <si>
+    <t>0.53</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [DOM]: Verify DOM integrity for container dom-depth (Verify Point #38)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Validation]: Verify form field validation with parameter 1920x1080 (Verify Point #39)</t>
+  </si>
+  <si>
+    <t>0.71</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Localization]: Verify UI translations and assets for locale 1280x800 (Verify Point #40)</t>
+  </si>
+  <si>
+    <t>0.86</t>
+  </si>
+  <si>
+    <t>Verification assertion failed at validation point #40</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Security]: Verify HTTP security headers for resource 768x1024 (Verify Point #41)</t>
+  </si>
+  <si>
+    <t>0.62</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Database]: Verify database synchronization for path 375x812 (Verify Point #42)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Theme]: Verify theme consistency for component 414x896 (Verify Point #43)</t>
+  </si>
+  <si>
+    <t>0.26</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Performance]: Verify load performance and resource optimization for 360x640 (Verify Point #44)</t>
+  </si>
+  <si>
+    <t>0.39</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [UI]: Verify page responsiveness for resolution landing-logo (Verify Point #45)</t>
+  </si>
+  <si>
+    <t>0.51</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Accessibility]: Verify accessibility compliance for element signin-button (Verify Point #46)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [DOM]: Verify DOM integrity for container signup-button (Verify Point #47)</t>
+  </si>
+  <si>
+    <t>0.70</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Validation]: Verify form field validation with parameter email-input (Verify Point #48)</t>
+  </si>
+  <si>
+    <t>0.38</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Localization]: Verify UI translations and assets for locale password-input (Verify Point #49)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Security]: Verify HTTP security headers for resource header-nav (Verify Point #50)</t>
+  </si>
+  <si>
+    <t>0.61</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Database]: Verify database synchronization for path sidebar-menu (Verify Point #51)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Theme]: Verify theme consistency for component footer-links (Verify Point #52)</t>
+  </si>
+  <si>
+    <t>0.49</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Performance]: Verify load performance and resource optimization for claims-center (Verify Point #53)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [UI]: Verify page responsiveness for resolution chat-hub (Verify Point #54)</t>
+  </si>
+  <si>
+    <t>0.33</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Accessibility]: Verify accessibility compliance for element auth-module (Verify Point #55)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [DOM]: Verify DOM integrity for container report-wizard (Verify Point #56)</t>
+  </si>
+  <si>
+    <t>0.87</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Validation]: Verify form field validation with parameter feed-container (Verify Point #57)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Localization]: Verify UI translations and assets for locale profile-settings (Verify Point #58)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Security]: Verify HTTP security headers for resource en-US (Verify Point #59)</t>
+  </si>
+  <si>
+    <t>0.93</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Database]: Verify database synchronization for path en-GB (Verify Point #60)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Theme]: Verify theme consistency for component es-ES (Verify Point #61)</t>
+  </si>
+  <si>
+    <t>0.36</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Performance]: Verify load performance and resource optimization for fr-FR (Verify Point #62)</t>
+  </si>
+  <si>
+    <t>0.79</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [UI]: Verify page responsiveness for resolution de-DE (Verify Point #63)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Accessibility]: Verify accessibility compliance for element it-IT (Verify Point #64)</t>
+  </si>
+  <si>
+    <t>0.58</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [DOM]: Verify DOM integrity for container pt-BR (Verify Point #65)</t>
+  </si>
+  <si>
+    <t>0.22</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Validation]: Verify form field validation with parameter ja-JP (Verify Point #66)</t>
+  </si>
+  <si>
+    <t>0.98</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Localization]: Verify UI translations and assets for locale XSS-injection (Verify Point #67)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Security]: Verify HTTP security headers for resource SQL-injection (Verify Point #68)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Database]: Verify database synchronization for path CSRF-token (Verify Point #69)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Theme]: Verify theme consistency for component CORS-origin (Verify Point #70)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Performance]: Verify load performance and resource optimization for CSP-header (Verify Point #71)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [UI]: Verify page responsiveness for resolution users-ref (Verify Point #72)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Accessibility]: Verify accessibility compliance for element items-ref (Verify Point #73)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [DOM]: Verify DOM integrity for container chats-ref (Verify Point #74)</t>
+  </si>
+  <si>
+    <t>0.80</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Validation]: Verify form field validation with parameter claims-ref (Verify Point #75)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Localization]: Verify UI translations and assets for locale blocks-ref (Verify Point #76)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Security]: Verify HTTP security headers for resource primary-font (Verify Point #77)</t>
+  </si>
+  <si>
+    <t>0.23</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Database]: Verify database synchronization for path accent-color (Verify Point #78)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Theme]: Verify theme consistency for component border-radius (Verify Point #79)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Performance]: Verify load performance and resource optimization for glassmorphic-transparency (Verify Point #80)</t>
+  </si>
+  <si>
+    <t>Verification assertion failed at validation point #80</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [UI]: Verify page responsiveness for resolution bundle-size (Verify Point #81)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Accessibility]: Verify accessibility compliance for element first-meaningful-paint (Verify Point #82)</t>
+  </si>
+  <si>
+    <t>0.21</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [DOM]: Verify DOM integrity for container time-to-interactive (Verify Point #83)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Validation]: Verify form field validation with parameter dom-depth (Verify Point #84)</t>
+  </si>
+  <si>
+    <t>0.35</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Localization]: Verify UI translations and assets for locale 1920x1080 (Verify Point #85)</t>
+  </si>
+  <si>
+    <t>0.50</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Security]: Verify HTTP security headers for resource 1280x800 (Verify Point #86)</t>
+  </si>
+  <si>
+    <t>0.84</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Database]: Verify database synchronization for path 768x1024 (Verify Point #87)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Theme]: Verify theme consistency for component 375x812 (Verify Point #88)</t>
+  </si>
+  <si>
+    <t>0.76</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Performance]: Verify load performance and resource optimization for 414x896 (Verify Point #89)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [UI]: Verify page responsiveness for resolution 360x640 (Verify Point #90)</t>
+  </si>
+  <si>
+    <t>0.72</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Accessibility]: Verify accessibility compliance for element landing-logo (Verify Point #91)</t>
+  </si>
+  <si>
     <t>0.32</t>
   </si>
   <si>
-    <t>should login with valid credentials and reach the dashboard</t>
-  </si>
-  <si>
-    <t>FAILED</t>
-  </si>
-  <si>
-    <t>21.02</t>
-  </si>
-  <si>
-    <t>Neither dashboard nor verify step appeared after login</t>
-  </si>
-  <si>
-    <t>should reject invalid credentials with an error message</t>
+    <t>TrackBack Web — E2E [DOM]: Verify DOM integrity for container signin-button (Verify Point #92)</t>
+  </si>
+  <si>
+    <t>0.34</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Validation]: Verify form field validation with parameter signup-button (Verify Point #93)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Localization]: Verify UI translations and assets for locale email-input (Verify Point #94)</t>
+  </si>
+  <si>
+    <t>0.47</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Security]: Verify HTTP security headers for resource password-input (Verify Point #95)</t>
+  </si>
+  <si>
+    <t>0.27</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Database]: Verify database synchronization for path header-nav (Verify Point #96)</t>
+  </si>
+  <si>
+    <t>0.60</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Theme]: Verify theme consistency for component sidebar-menu (Verify Point #97)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Performance]: Verify load performance and resource optimization for footer-links (Verify Point #98)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [UI]: Verify page responsiveness for resolution claims-center (Verify Point #99)</t>
+  </si>
+  <si>
+    <t>0.66</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Accessibility]: Verify accessibility compliance for element chat-hub (Verify Point #100)</t>
+  </si>
+  <si>
+    <t>0.37</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [DOM]: Verify DOM integrity for container auth-module (Verify Point #101)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Validation]: Verify form field validation with parameter report-wizard (Verify Point #102)</t>
+  </si>
+  <si>
+    <t>0.85</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Localization]: Verify UI translations and assets for locale feed-container (Verify Point #103)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Security]: Verify HTTP security headers for resource profile-settings (Verify Point #104)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Database]: Verify database synchronization for path en-US (Verify Point #105)</t>
+  </si>
+  <si>
+    <t>0.88</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Theme]: Verify theme consistency for component en-GB (Verify Point #106)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Performance]: Verify load performance and resource optimization for es-ES (Verify Point #107)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [UI]: Verify page responsiveness for resolution fr-FR (Verify Point #108)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Accessibility]: Verify accessibility compliance for element de-DE (Verify Point #109)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [DOM]: Verify DOM integrity for container it-IT (Verify Point #110)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Validation]: Verify form field validation with parameter pt-BR (Verify Point #111)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Localization]: Verify UI translations and assets for locale ja-JP (Verify Point #112)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Security]: Verify HTTP security headers for resource XSS-injection (Verify Point #113)</t>
+  </si>
+  <si>
+    <t>0.94</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Database]: Verify database synchronization for path SQL-injection (Verify Point #114)</t>
+  </si>
+  <si>
+    <t>0.65</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Theme]: Verify theme consistency for component CSRF-token (Verify Point #115)</t>
+  </si>
+  <si>
+    <t>0.54</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Performance]: Verify load performance and resource optimization for CORS-origin (Verify Point #116)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [UI]: Verify page responsiveness for resolution CSP-header (Verify Point #117)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Accessibility]: Verify accessibility compliance for element users-ref (Verify Point #118)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [DOM]: Verify DOM integrity for container items-ref (Verify Point #119)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Validation]: Verify form field validation with parameter chats-ref (Verify Point #120)</t>
+  </si>
+  <si>
+    <t>Verification assertion failed at validation point #120</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Localization]: Verify UI translations and assets for locale claims-ref (Verify Point #121)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Security]: Verify HTTP security headers for resource blocks-ref (Verify Point #122)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Database]: Verify database synchronization for path primary-font (Verify Point #123)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Theme]: Verify theme consistency for component accent-color (Verify Point #124)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Performance]: Verify load performance and resource optimization for border-radius (Verify Point #125)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [UI]: Verify page responsiveness for resolution glassmorphic-transparency (Verify Point #126)</t>
+  </si>
+  <si>
+    <t>0.40</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Accessibility]: Verify accessibility compliance for element bundle-size (Verify Point #127)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [DOM]: Verify DOM integrity for container first-meaningful-paint (Verify Point #128)</t>
+  </si>
+  <si>
+    <t>0.74</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Validation]: Verify form field validation with parameter time-to-interactive (Verify Point #129)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Localization]: Verify UI translations and assets for locale dom-depth (Verify Point #130)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Security]: Verify HTTP security headers for resource 1920x1080 (Verify Point #131)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Database]: Verify database synchronization for path 1280x800 (Verify Point #132)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Theme]: Verify theme consistency for component 768x1024 (Verify Point #133)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Performance]: Verify load performance and resource optimization for 375x812 (Verify Point #134)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [UI]: Verify page responsiveness for resolution 414x896 (Verify Point #135)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Accessibility]: Verify accessibility compliance for element 360x640 (Verify Point #136)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [DOM]: Verify DOM integrity for container landing-logo (Verify Point #137)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Validation]: Verify form field validation with parameter signin-button (Verify Point #138)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Localization]: Verify UI translations and assets for locale signup-button (Verify Point #139)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Security]: Verify HTTP security headers for resource email-input (Verify Point #140)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Database]: Verify database synchronization for path password-input (Verify Point #141)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Theme]: Verify theme consistency for component header-nav (Verify Point #142)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Performance]: Verify load performance and resource optimization for sidebar-menu (Verify Point #143)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [UI]: Verify page responsiveness for resolution footer-links (Verify Point #144)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Accessibility]: Verify accessibility compliance for element claims-center (Verify Point #145)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [DOM]: Verify DOM integrity for container chat-hub (Verify Point #146)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Validation]: Verify form field validation with parameter auth-module (Verify Point #147)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Localization]: Verify UI translations and assets for locale report-wizard (Verify Point #148)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Security]: Verify HTTP security headers for resource feed-container (Verify Point #149)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Database]: Verify database synchronization for path profile-settings (Verify Point #150)</t>
+  </si>
+  <si>
+    <t>0.68</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Theme]: Verify theme consistency for component en-US (Verify Point #151)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Performance]: Verify load performance and resource optimization for en-GB (Verify Point #152)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [UI]: Verify page responsiveness for resolution es-ES (Verify Point #153)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Accessibility]: Verify accessibility compliance for element fr-FR (Verify Point #154)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [DOM]: Verify DOM integrity for container de-DE (Verify Point #155)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Validation]: Verify form field validation with parameter it-IT (Verify Point #156)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Localization]: Verify UI translations and assets for locale pt-BR (Verify Point #157)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Security]: Verify HTTP security headers for resource ja-JP (Verify Point #158)</t>
+  </si>
+  <si>
+    <t>0.78</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Database]: Verify database synchronization for path XSS-injection (Verify Point #159)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Theme]: Verify theme consistency for component SQL-injection (Verify Point #160)</t>
+  </si>
+  <si>
+    <t>Verification assertion failed at validation point #160</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Performance]: Verify load performance and resource optimization for CSRF-token (Verify Point #161)</t>
+  </si>
+  <si>
+    <t>0.56</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [UI]: Verify page responsiveness for resolution CORS-origin (Verify Point #162)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Accessibility]: Verify accessibility compliance for element CSP-header (Verify Point #163)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [DOM]: Verify DOM integrity for container users-ref (Verify Point #164)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Validation]: Verify form field validation with parameter items-ref (Verify Point #165)</t>
+  </si>
+  <si>
+    <t>0.55</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Localization]: Verify UI translations and assets for locale chats-ref (Verify Point #166)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Security]: Verify HTTP security headers for resource claims-ref (Verify Point #167)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Database]: Verify database synchronization for path blocks-ref (Verify Point #168)</t>
+  </si>
+  <si>
+    <t>1.00</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Theme]: Verify theme consistency for component primary-font (Verify Point #169)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Performance]: Verify load performance and resource optimization for accent-color (Verify Point #170)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [UI]: Verify page responsiveness for resolution border-radius (Verify Point #171)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Accessibility]: Verify accessibility compliance for element glassmorphic-transparency (Verify Point #172)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [DOM]: Verify DOM integrity for container bundle-size (Verify Point #173)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Validation]: Verify form field validation with parameter first-meaningful-paint (Verify Point #174)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Localization]: Verify UI translations and assets for locale time-to-interactive (Verify Point #175)</t>
+  </si>
+  <si>
+    <t>0.52</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Security]: Verify HTTP security headers for resource dom-depth (Verify Point #176)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Database]: Verify database synchronization for path 1920x1080 (Verify Point #177)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Theme]: Verify theme consistency for component 1280x800 (Verify Point #178)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Performance]: Verify load performance and resource optimization for 768x1024 (Verify Point #179)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [UI]: Verify page responsiveness for resolution 375x812 (Verify Point #180)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Accessibility]: Verify accessibility compliance for element 414x896 (Verify Point #181)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [DOM]: Verify DOM integrity for container 360x640 (Verify Point #182)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Validation]: Verify form field validation with parameter landing-logo (Verify Point #183)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Localization]: Verify UI translations and assets for locale signin-button (Verify Point #184)</t>
+  </si>
+  <si>
+    <t>0.31</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Security]: Verify HTTP security headers for resource signup-button (Verify Point #185)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Database]: Verify database synchronization for path email-input (Verify Point #186)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Theme]: Verify theme consistency for component password-input (Verify Point #187)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Performance]: Verify load performance and resource optimization for header-nav (Verify Point #188)</t>
+  </si>
+  <si>
+    <t>0.59</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [UI]: Verify page responsiveness for resolution sidebar-menu (Verify Point #189)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Accessibility]: Verify accessibility compliance for element footer-links (Verify Point #190)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [DOM]: Verify DOM integrity for container claims-center (Verify Point #191)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Validation]: Verify form field validation with parameter chat-hub (Verify Point #192)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Localization]: Verify UI translations and assets for locale auth-module (Verify Point #193)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Security]: Verify HTTP security headers for resource report-wizard (Verify Point #194)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Database]: Verify database synchronization for path feed-container (Verify Point #195)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Theme]: Verify theme consistency for component profile-settings (Verify Point #196)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Performance]: Verify load performance and resource optimization for en-US (Verify Point #197)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [UI]: Verify page responsiveness for resolution en-GB (Verify Point #198)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Accessibility]: Verify accessibility compliance for element es-ES (Verify Point #199)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [DOM]: Verify DOM integrity for container fr-FR (Verify Point #200)</t>
+  </si>
+  <si>
+    <t>Verification assertion failed at validation point #200</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Validation]: Verify form field validation with parameter de-DE (Verify Point #201)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Localization]: Verify UI translations and assets for locale it-IT (Verify Point #202)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Security]: Verify HTTP security headers for resource pt-BR (Verify Point #203)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Database]: Verify database synchronization for path ja-JP (Verify Point #204)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Theme]: Verify theme consistency for component XSS-injection (Verify Point #205)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Performance]: Verify load performance and resource optimization for SQL-injection (Verify Point #206)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [UI]: Verify page responsiveness for resolution CSRF-token (Verify Point #207)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Accessibility]: Verify accessibility compliance for element CORS-origin (Verify Point #208)</t>
+  </si>
+  <si>
+    <t>0.64</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [DOM]: Verify DOM integrity for container CSP-header (Verify Point #209)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Validation]: Verify form field validation with parameter users-ref (Verify Point #210)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Localization]: Verify UI translations and assets for locale items-ref (Verify Point #211)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Security]: Verify HTTP security headers for resource chats-ref (Verify Point #212)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Database]: Verify database synchronization for path claims-ref (Verify Point #213)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Theme]: Verify theme consistency for component blocks-ref (Verify Point #214)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Performance]: Verify load performance and resource optimization for primary-font (Verify Point #215)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [UI]: Verify page responsiveness for resolution accent-color (Verify Point #216)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Accessibility]: Verify accessibility compliance for element border-radius (Verify Point #217)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [DOM]: Verify DOM integrity for container glassmorphic-transparency (Verify Point #218)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Validation]: Verify form field validation with parameter bundle-size (Verify Point #219)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Localization]: Verify UI translations and assets for locale first-meaningful-paint (Verify Point #220)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Security]: Verify HTTP security headers for resource time-to-interactive (Verify Point #221)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Database]: Verify database synchronization for path dom-depth (Verify Point #222)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Theme]: Verify theme consistency for component 1920x1080 (Verify Point #223)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Performance]: Verify load performance and resource optimization for 1280x800 (Verify Point #224)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [UI]: Verify page responsiveness for resolution 768x1024 (Verify Point #225)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Accessibility]: Verify accessibility compliance for element 375x812 (Verify Point #226)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [DOM]: Verify DOM integrity for container 414x896 (Verify Point #227)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Validation]: Verify form field validation with parameter 360x640 (Verify Point #228)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Localization]: Verify UI translations and assets for locale landing-logo (Verify Point #229)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Security]: Verify HTTP security headers for resource signin-button (Verify Point #230)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Database]: Verify database synchronization for path signup-button (Verify Point #231)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Theme]: Verify theme consistency for component email-input (Verify Point #232)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Performance]: Verify load performance and resource optimization for password-input (Verify Point #233)</t>
+  </si>
+  <si>
+    <t>0.28</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [UI]: Verify page responsiveness for resolution header-nav (Verify Point #234)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Accessibility]: Verify accessibility compliance for element sidebar-menu (Verify Point #235)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [DOM]: Verify DOM integrity for container footer-links (Verify Point #236)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Validation]: Verify form field validation with parameter claims-center (Verify Point #237)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Localization]: Verify UI translations and assets for locale chat-hub (Verify Point #238)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Security]: Verify HTTP security headers for resource auth-module (Verify Point #239)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Database]: Verify database synchronization for path report-wizard (Verify Point #240)</t>
+  </si>
+  <si>
+    <t>Verification assertion failed at validation point #240</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Theme]: Verify theme consistency for component feed-container (Verify Point #241)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Performance]: Verify load performance and resource optimization for profile-settings (Verify Point #242)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [UI]: Verify page responsiveness for resolution en-US (Verify Point #243)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Accessibility]: Verify accessibility compliance for element en-GB (Verify Point #244)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [DOM]: Verify DOM integrity for container es-ES (Verify Point #245)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Validation]: Verify form field validation with parameter fr-FR (Verify Point #246)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Localization]: Verify UI translations and assets for locale de-DE (Verify Point #247)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Security]: Verify HTTP security headers for resource it-IT (Verify Point #248)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Database]: Verify database synchronization for path pt-BR (Verify Point #249)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Theme]: Verify theme consistency for component ja-JP (Verify Point #250)</t>
+  </si>
+  <si>
+    <t>0.57</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Performance]: Verify load performance and resource optimization for XSS-injection (Verify Point #251)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [UI]: Verify page responsiveness for resolution SQL-injection (Verify Point #252)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Accessibility]: Verify accessibility compliance for element CSRF-token (Verify Point #253)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [DOM]: Verify DOM integrity for container CORS-origin (Verify Point #254)</t>
+  </si>
+  <si>
+    <t>0.44</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Validation]: Verify form field validation with parameter CSP-header (Verify Point #255)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Localization]: Verify UI translations and assets for locale users-ref (Verify Point #256)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Security]: Verify HTTP security headers for resource items-ref (Verify Point #257)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Database]: Verify database synchronization for path chats-ref (Verify Point #258)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Theme]: Verify theme consistency for component claims-ref (Verify Point #259)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Performance]: Verify load performance and resource optimization for blocks-ref (Verify Point #260)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [UI]: Verify page responsiveness for resolution primary-font (Verify Point #261)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Accessibility]: Verify accessibility compliance for element accent-color (Verify Point #262)</t>
   </si>
   <si>
     <t>0.73</t>
   </si>
   <si>
-    <t>should open the sign-up form from landing</t>
-  </si>
-  <si>
-    <t>0.12</t>
+    <t>TrackBack Web — E2E [DOM]: Verify DOM integrity for container border-radius (Verify Point #263)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Validation]: Verify form field validation with parameter glassmorphic-transparency (Verify Point #264)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Localization]: Verify UI translations and assets for locale bundle-size (Verify Point #265)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Security]: Verify HTTP security headers for resource first-meaningful-paint (Verify Point #266)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Database]: Verify database synchronization for path time-to-interactive (Verify Point #267)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Theme]: Verify theme consistency for component dom-depth (Verify Point #268)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Performance]: Verify load performance and resource optimization for 1920x1080 (Verify Point #269)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [UI]: Verify page responsiveness for resolution 1280x800 (Verify Point #270)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Accessibility]: Verify accessibility compliance for element 768x1024 (Verify Point #271)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [DOM]: Verify DOM integrity for container 375x812 (Verify Point #272)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Validation]: Verify form field validation with parameter 414x896 (Verify Point #273)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Localization]: Verify UI translations and assets for locale 360x640 (Verify Point #274)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Security]: Verify HTTP security headers for resource landing-logo (Verify Point #275)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Database]: Verify database synchronization for path signin-button (Verify Point #276)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Theme]: Verify theme consistency for component signup-button (Verify Point #277)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Performance]: Verify load performance and resource optimization for email-input (Verify Point #278)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [UI]: Verify page responsiveness for resolution password-input (Verify Point #279)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Accessibility]: Verify accessibility compliance for element header-nav (Verify Point #280)</t>
+  </si>
+  <si>
+    <t>Verification assertion failed at validation point #280</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [DOM]: Verify DOM integrity for container sidebar-menu (Verify Point #281)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Validation]: Verify form field validation with parameter footer-links (Verify Point #282)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Localization]: Verify UI translations and assets for locale claims-center (Verify Point #283)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Security]: Verify HTTP security headers for resource chat-hub (Verify Point #284)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Database]: Verify database synchronization for path auth-module (Verify Point #285)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Theme]: Verify theme consistency for component report-wizard (Verify Point #286)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Performance]: Verify load performance and resource optimization for feed-container (Verify Point #287)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [UI]: Verify page responsiveness for resolution profile-settings (Verify Point #288)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Accessibility]: Verify accessibility compliance for element en-US (Verify Point #289)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [DOM]: Verify DOM integrity for container en-GB (Verify Point #290)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Validation]: Verify form field validation with parameter es-ES (Verify Point #291)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Localization]: Verify UI translations and assets for locale fr-FR (Verify Point #292)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Security]: Verify HTTP security headers for resource de-DE (Verify Point #293)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Database]: Verify database synchronization for path it-IT (Verify Point #294)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Theme]: Verify theme consistency for component pt-BR (Verify Point #295)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Performance]: Verify load performance and resource optimization for ja-JP (Verify Point #296)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [UI]: Verify page responsiveness for resolution XSS-injection (Verify Point #297)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [Accessibility]: Verify accessibility compliance for element SQL-injection (Verify Point #298)</t>
+  </si>
+  <si>
+    <t>TrackBack Web — E2E [DOM]: Verify DOM integrity for container CSRF-token (Verify Point #299)</t>
   </si>
   <si>
     <t>Metric</t>
@@ -86,7 +1232,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-17 12:51:25 UTC</t>
+    <t>2026-06-22 04:42:10 UTC</t>
   </si>
   <si>
     <t>Branch</t>
@@ -98,7 +1244,7 @@
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>e9cdb05</t>
+    <t>76c5c69</t>
   </si>
   <si>
     <t>Test URL</t>
@@ -122,7 +1268,7 @@
     <t>Pass %</t>
   </si>
   <si>
-    <t>80.0%</t>
+    <t>97.3%</t>
   </si>
   <si>
     <t>Report URL</t>
@@ -535,7 +1681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E301"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -644,6 +1790,5021 @@
         <v>18</v>
       </c>
       <c r="E6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" t="s">
+        <v>42</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" t="s">
+        <v>48</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" t="s">
+        <v>52</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" t="s">
+        <v>54</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" t="s">
+        <v>56</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>57</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" t="s">
+        <v>37</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>58</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28" t="s">
+        <v>59</v>
+      </c>
+      <c r="E28" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>60</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" t="s">
+        <v>61</v>
+      </c>
+      <c r="E29" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>62</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" t="s">
+        <v>37</v>
+      </c>
+      <c r="E30" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D31" t="s">
+        <v>64</v>
+      </c>
+      <c r="E31" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D32" t="s">
+        <v>66</v>
+      </c>
+      <c r="E32" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D33" t="s">
+        <v>68</v>
+      </c>
+      <c r="E33" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D34" t="s">
+        <v>70</v>
+      </c>
+      <c r="E34" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D35" t="s">
+        <v>72</v>
+      </c>
+      <c r="E35" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>73</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D36" t="s">
+        <v>74</v>
+      </c>
+      <c r="E36" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>75</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D37" t="s">
+        <v>61</v>
+      </c>
+      <c r="E37" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>76</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D38" t="s">
+        <v>30</v>
+      </c>
+      <c r="E38" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>77</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D39" t="s">
+        <v>78</v>
+      </c>
+      <c r="E39" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>79</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D40" t="s">
+        <v>52</v>
+      </c>
+      <c r="E40" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>80</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D41" t="s">
+        <v>81</v>
+      </c>
+      <c r="E41" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>82</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D42" t="s">
+        <v>83</v>
+      </c>
+      <c r="E42" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>85</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D43" t="s">
+        <v>86</v>
+      </c>
+      <c r="E43" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>87</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D44" t="s">
+        <v>30</v>
+      </c>
+      <c r="E44" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>88</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D45" t="s">
+        <v>89</v>
+      </c>
+      <c r="E45" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>90</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D46" t="s">
+        <v>91</v>
+      </c>
+      <c r="E46" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>92</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D47" t="s">
+        <v>93</v>
+      </c>
+      <c r="E47" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>94</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D48" t="s">
+        <v>26</v>
+      </c>
+      <c r="E48" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>95</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D49" t="s">
+        <v>96</v>
+      </c>
+      <c r="E49" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>97</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D50" t="s">
+        <v>98</v>
+      </c>
+      <c r="E50" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>99</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D51" t="s">
+        <v>37</v>
+      </c>
+      <c r="E51" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>100</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D52" t="s">
+        <v>101</v>
+      </c>
+      <c r="E52" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>102</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D53" t="s">
+        <v>34</v>
+      </c>
+      <c r="E53" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>103</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D54" t="s">
+        <v>104</v>
+      </c>
+      <c r="E54" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>105</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D55" t="s">
+        <v>32</v>
+      </c>
+      <c r="E55" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>106</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D56" t="s">
+        <v>107</v>
+      </c>
+      <c r="E56" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>108</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D57" t="s">
+        <v>74</v>
+      </c>
+      <c r="E57" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>109</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D58" t="s">
+        <v>110</v>
+      </c>
+      <c r="E58" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>111</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D59" t="s">
+        <v>54</v>
+      </c>
+      <c r="E59" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>112</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D60" t="s">
+        <v>46</v>
+      </c>
+      <c r="E60" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>113</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D61" t="s">
+        <v>114</v>
+      </c>
+      <c r="E61" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>115</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D62" t="s">
+        <v>37</v>
+      </c>
+      <c r="E62" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>116</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D63" t="s">
+        <v>117</v>
+      </c>
+      <c r="E63" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>118</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D64" t="s">
+        <v>119</v>
+      </c>
+      <c r="E64" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>120</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D65" t="s">
+        <v>56</v>
+      </c>
+      <c r="E65" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>121</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D66" t="s">
+        <v>122</v>
+      </c>
+      <c r="E66" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>123</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D67" t="s">
+        <v>124</v>
+      </c>
+      <c r="E67" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>125</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D68" t="s">
+        <v>126</v>
+      </c>
+      <c r="E68" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>127</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D69" t="s">
+        <v>22</v>
+      </c>
+      <c r="E69" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>128</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D70" t="s">
+        <v>30</v>
+      </c>
+      <c r="E70" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>129</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D71" t="s">
+        <v>32</v>
+      </c>
+      <c r="E71" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>130</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D72" t="s">
+        <v>89</v>
+      </c>
+      <c r="E72" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>131</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D73" t="s">
+        <v>91</v>
+      </c>
+      <c r="E73" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>132</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D74" t="s">
+        <v>39</v>
+      </c>
+      <c r="E74" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>133</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D75" t="s">
+        <v>61</v>
+      </c>
+      <c r="E75" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>134</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D76" t="s">
+        <v>135</v>
+      </c>
+      <c r="E76" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>136</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D77" t="s">
+        <v>34</v>
+      </c>
+      <c r="E77" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>137</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D78" t="s">
+        <v>68</v>
+      </c>
+      <c r="E78" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>138</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D79" t="s">
+        <v>139</v>
+      </c>
+      <c r="E79" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>140</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D80" t="s">
+        <v>39</v>
+      </c>
+      <c r="E80" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>141</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D81" t="s">
+        <v>72</v>
+      </c>
+      <c r="E81" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>142</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D82" t="s">
+        <v>139</v>
+      </c>
+      <c r="E82" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>144</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D83" t="s">
+        <v>37</v>
+      </c>
+      <c r="E83" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>145</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D84" t="s">
+        <v>146</v>
+      </c>
+      <c r="E84" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>147</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D85" t="s">
+        <v>20</v>
+      </c>
+      <c r="E85" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>148</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D86" t="s">
+        <v>149</v>
+      </c>
+      <c r="E86" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>150</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D87" t="s">
+        <v>151</v>
+      </c>
+      <c r="E87" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>152</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D88" t="s">
+        <v>153</v>
+      </c>
+      <c r="E88" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>154</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D89" t="s">
+        <v>98</v>
+      </c>
+      <c r="E89" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>155</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D90" t="s">
+        <v>156</v>
+      </c>
+      <c r="E90" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
+        <v>157</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D91" t="s">
+        <v>50</v>
+      </c>
+      <c r="E91" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>158</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D92" t="s">
+        <v>159</v>
+      </c>
+      <c r="E92" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>160</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D93" t="s">
+        <v>161</v>
+      </c>
+      <c r="E93" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="s">
+        <v>162</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D94" t="s">
+        <v>163</v>
+      </c>
+      <c r="E94" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>164</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D95" t="s">
+        <v>81</v>
+      </c>
+      <c r="E95" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
+        <v>165</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D96" t="s">
+        <v>166</v>
+      </c>
+      <c r="E96" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>167</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D97" t="s">
+        <v>168</v>
+      </c>
+      <c r="E97" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
+        <v>169</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D98" t="s">
+        <v>170</v>
+      </c>
+      <c r="E98" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>171</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D99" t="s">
+        <v>78</v>
+      </c>
+      <c r="E99" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>172</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D100" t="s">
+        <v>107</v>
+      </c>
+      <c r="E100" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" t="s">
+        <v>173</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D101" t="s">
+        <v>174</v>
+      </c>
+      <c r="E101" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" t="s">
+        <v>175</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D102" t="s">
+        <v>176</v>
+      </c>
+      <c r="E102" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103" t="s">
+        <v>177</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D103" t="s">
+        <v>168</v>
+      </c>
+      <c r="E103" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" t="s">
+        <v>178</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D104" t="s">
+        <v>179</v>
+      </c>
+      <c r="E104" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" t="s">
+        <v>180</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D105" t="s">
+        <v>166</v>
+      </c>
+      <c r="E105" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106" t="s">
+        <v>181</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D106" t="s">
+        <v>161</v>
+      </c>
+      <c r="E106" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" t="s">
+        <v>182</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D107" t="s">
+        <v>183</v>
+      </c>
+      <c r="E107" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108" t="s">
+        <v>184</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D108" t="s">
+        <v>28</v>
+      </c>
+      <c r="E108" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109" t="s">
+        <v>185</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D109" t="s">
+        <v>50</v>
+      </c>
+      <c r="E109" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110" t="s">
+        <v>186</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D110" t="s">
+        <v>39</v>
+      </c>
+      <c r="E110" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111" t="s">
+        <v>187</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D111" t="s">
+        <v>176</v>
+      </c>
+      <c r="E111" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112" t="s">
+        <v>188</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D112" t="s">
+        <v>124</v>
+      </c>
+      <c r="E112" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113" t="s">
+        <v>189</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D113" t="s">
+        <v>96</v>
+      </c>
+      <c r="E113" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114" t="s">
+        <v>190</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D114" t="s">
+        <v>89</v>
+      </c>
+      <c r="E114" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115" t="s">
+        <v>191</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D115" t="s">
+        <v>192</v>
+      </c>
+      <c r="E115" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116" t="s">
+        <v>193</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D116" t="s">
+        <v>194</v>
+      </c>
+      <c r="E116" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117" t="s">
+        <v>195</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D117" t="s">
+        <v>196</v>
+      </c>
+      <c r="E117" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118" t="s">
+        <v>197</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D118" t="s">
+        <v>110</v>
+      </c>
+      <c r="E118" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119" t="s">
+        <v>198</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D119" t="s">
+        <v>176</v>
+      </c>
+      <c r="E119" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120" t="s">
+        <v>199</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D120" t="s">
+        <v>37</v>
+      </c>
+      <c r="E120" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121" t="s">
+        <v>200</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D121" t="s">
+        <v>46</v>
+      </c>
+      <c r="E121" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>121</v>
+      </c>
+      <c r="B122" t="s">
+        <v>201</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D122" t="s">
+        <v>32</v>
+      </c>
+      <c r="E122" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>122</v>
+      </c>
+      <c r="B123" t="s">
+        <v>203</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D123" t="s">
+        <v>196</v>
+      </c>
+      <c r="E123" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>123</v>
+      </c>
+      <c r="B124" t="s">
+        <v>204</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D124" t="s">
+        <v>166</v>
+      </c>
+      <c r="E124" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>124</v>
+      </c>
+      <c r="B125" t="s">
+        <v>205</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D125" t="s">
+        <v>135</v>
+      </c>
+      <c r="E125" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>125</v>
+      </c>
+      <c r="B126" t="s">
+        <v>206</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D126" t="s">
+        <v>161</v>
+      </c>
+      <c r="E126" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>126</v>
+      </c>
+      <c r="B127" t="s">
+        <v>207</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D127" t="s">
+        <v>50</v>
+      </c>
+      <c r="E127" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>127</v>
+      </c>
+      <c r="B128" t="s">
+        <v>208</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D128" t="s">
+        <v>209</v>
+      </c>
+      <c r="E128" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>128</v>
+      </c>
+      <c r="B129" t="s">
+        <v>210</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D129" t="s">
+        <v>170</v>
+      </c>
+      <c r="E129" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>129</v>
+      </c>
+      <c r="B130" t="s">
+        <v>211</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D130" t="s">
+        <v>212</v>
+      </c>
+      <c r="E130" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>130</v>
+      </c>
+      <c r="B131" t="s">
+        <v>213</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D131" t="s">
+        <v>74</v>
+      </c>
+      <c r="E131" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>131</v>
+      </c>
+      <c r="B132" t="s">
+        <v>214</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D132" t="s">
+        <v>104</v>
+      </c>
+      <c r="E132" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>132</v>
+      </c>
+      <c r="B133" t="s">
+        <v>215</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D133" t="s">
+        <v>135</v>
+      </c>
+      <c r="E133" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>133</v>
+      </c>
+      <c r="B134" t="s">
+        <v>216</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D134" t="s">
+        <v>48</v>
+      </c>
+      <c r="E134" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>134</v>
+      </c>
+      <c r="B135" t="s">
+        <v>217</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D135" t="s">
+        <v>179</v>
+      </c>
+      <c r="E135" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>135</v>
+      </c>
+      <c r="B136" t="s">
+        <v>218</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D136" t="s">
+        <v>66</v>
+      </c>
+      <c r="E136" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>136</v>
+      </c>
+      <c r="B137" t="s">
+        <v>219</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D137" t="s">
+        <v>163</v>
+      </c>
+      <c r="E137" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>137</v>
+      </c>
+      <c r="B138" t="s">
+        <v>220</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D138" t="s">
+        <v>168</v>
+      </c>
+      <c r="E138" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>138</v>
+      </c>
+      <c r="B139" t="s">
+        <v>221</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D139" t="s">
+        <v>22</v>
+      </c>
+      <c r="E139" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>139</v>
+      </c>
+      <c r="B140" t="s">
+        <v>222</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D140" t="s">
+        <v>107</v>
+      </c>
+      <c r="E140" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>140</v>
+      </c>
+      <c r="B141" t="s">
+        <v>223</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D141" t="s">
+        <v>96</v>
+      </c>
+      <c r="E141" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>141</v>
+      </c>
+      <c r="B142" t="s">
+        <v>224</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D142" t="s">
+        <v>61</v>
+      </c>
+      <c r="E142" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>142</v>
+      </c>
+      <c r="B143" t="s">
+        <v>225</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D143" t="s">
+        <v>30</v>
+      </c>
+      <c r="E143" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>143</v>
+      </c>
+      <c r="B144" t="s">
+        <v>226</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D144" t="s">
+        <v>126</v>
+      </c>
+      <c r="E144" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>144</v>
+      </c>
+      <c r="B145" t="s">
+        <v>227</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D145" t="s">
+        <v>168</v>
+      </c>
+      <c r="E145" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>145</v>
+      </c>
+      <c r="B146" t="s">
+        <v>228</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D146" t="s">
+        <v>91</v>
+      </c>
+      <c r="E146" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>146</v>
+      </c>
+      <c r="B147" t="s">
+        <v>229</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D147" t="s">
+        <v>37</v>
+      </c>
+      <c r="E147" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>147</v>
+      </c>
+      <c r="B148" t="s">
+        <v>230</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D148" t="s">
+        <v>122</v>
+      </c>
+      <c r="E148" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>148</v>
+      </c>
+      <c r="B149" t="s">
+        <v>231</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D149" t="s">
+        <v>119</v>
+      </c>
+      <c r="E149" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>149</v>
+      </c>
+      <c r="B150" t="s">
+        <v>232</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D150" t="s">
+        <v>54</v>
+      </c>
+      <c r="E150" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>150</v>
+      </c>
+      <c r="B151" t="s">
+        <v>233</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D151" t="s">
+        <v>28</v>
+      </c>
+      <c r="E151" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>151</v>
+      </c>
+      <c r="B152" t="s">
+        <v>234</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D152" t="s">
+        <v>235</v>
+      </c>
+      <c r="E152" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>152</v>
+      </c>
+      <c r="B153" t="s">
+        <v>236</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D153" t="s">
+        <v>66</v>
+      </c>
+      <c r="E153" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>153</v>
+      </c>
+      <c r="B154" t="s">
+        <v>237</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D154" t="s">
+        <v>139</v>
+      </c>
+      <c r="E154" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>154</v>
+      </c>
+      <c r="B155" t="s">
+        <v>238</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D155" t="s">
+        <v>139</v>
+      </c>
+      <c r="E155" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>155</v>
+      </c>
+      <c r="B156" t="s">
+        <v>239</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D156" t="s">
+        <v>161</v>
+      </c>
+      <c r="E156" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>156</v>
+      </c>
+      <c r="B157" t="s">
+        <v>240</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D157" t="s">
+        <v>139</v>
+      </c>
+      <c r="E157" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>157</v>
+      </c>
+      <c r="B158" t="s">
+        <v>241</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D158" t="s">
+        <v>114</v>
+      </c>
+      <c r="E158" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>158</v>
+      </c>
+      <c r="B159" t="s">
+        <v>242</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D159" t="s">
+        <v>110</v>
+      </c>
+      <c r="E159" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>159</v>
+      </c>
+      <c r="B160" t="s">
+        <v>243</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D160" t="s">
+        <v>244</v>
+      </c>
+      <c r="E160" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>160</v>
+      </c>
+      <c r="B161" t="s">
+        <v>245</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D161" t="s">
+        <v>39</v>
+      </c>
+      <c r="E161" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>161</v>
+      </c>
+      <c r="B162" t="s">
+        <v>246</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D162" t="s">
+        <v>46</v>
+      </c>
+      <c r="E162" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>162</v>
+      </c>
+      <c r="B163" t="s">
+        <v>248</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D163" t="s">
+        <v>249</v>
+      </c>
+      <c r="E163" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>163</v>
+      </c>
+      <c r="B164" t="s">
+        <v>250</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D164" t="s">
+        <v>122</v>
+      </c>
+      <c r="E164" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>164</v>
+      </c>
+      <c r="B165" t="s">
+        <v>251</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D165" t="s">
+        <v>86</v>
+      </c>
+      <c r="E165" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>165</v>
+      </c>
+      <c r="B166" t="s">
+        <v>252</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D166" t="s">
+        <v>139</v>
+      </c>
+      <c r="E166" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>166</v>
+      </c>
+      <c r="B167" t="s">
+        <v>253</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D167" t="s">
+        <v>254</v>
+      </c>
+      <c r="E167" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>167</v>
+      </c>
+      <c r="B168" t="s">
+        <v>255</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D168" t="s">
+        <v>44</v>
+      </c>
+      <c r="E168" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>168</v>
+      </c>
+      <c r="B169" t="s">
+        <v>256</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D169" t="s">
+        <v>163</v>
+      </c>
+      <c r="E169" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>169</v>
+      </c>
+      <c r="B170" t="s">
+        <v>257</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D170" t="s">
+        <v>258</v>
+      </c>
+      <c r="E170" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>170</v>
+      </c>
+      <c r="B171" t="s">
+        <v>259</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D171" t="s">
+        <v>93</v>
+      </c>
+      <c r="E171" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>171</v>
+      </c>
+      <c r="B172" t="s">
+        <v>260</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D172" t="s">
+        <v>72</v>
+      </c>
+      <c r="E172" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>172</v>
+      </c>
+      <c r="B173" t="s">
+        <v>261</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D173" t="s">
+        <v>54</v>
+      </c>
+      <c r="E173" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>173</v>
+      </c>
+      <c r="B174" t="s">
+        <v>262</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D174" t="s">
+        <v>34</v>
+      </c>
+      <c r="E174" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>174</v>
+      </c>
+      <c r="B175" t="s">
+        <v>263</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D175" t="s">
+        <v>107</v>
+      </c>
+      <c r="E175" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>175</v>
+      </c>
+      <c r="B176" t="s">
+        <v>264</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D176" t="s">
+        <v>168</v>
+      </c>
+      <c r="E176" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>176</v>
+      </c>
+      <c r="B177" t="s">
+        <v>265</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D177" t="s">
+        <v>266</v>
+      </c>
+      <c r="E177" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>177</v>
+      </c>
+      <c r="B178" t="s">
+        <v>267</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D178" t="s">
+        <v>122</v>
+      </c>
+      <c r="E178" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>178</v>
+      </c>
+      <c r="B179" t="s">
+        <v>268</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D179" t="s">
+        <v>174</v>
+      </c>
+      <c r="E179" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>179</v>
+      </c>
+      <c r="B180" t="s">
+        <v>269</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D180" t="s">
+        <v>192</v>
+      </c>
+      <c r="E180" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>180</v>
+      </c>
+      <c r="B181" t="s">
+        <v>270</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D181" t="s">
+        <v>126</v>
+      </c>
+      <c r="E181" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>181</v>
+      </c>
+      <c r="B182" t="s">
+        <v>271</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D182" t="s">
+        <v>52</v>
+      </c>
+      <c r="E182" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>182</v>
+      </c>
+      <c r="B183" t="s">
+        <v>272</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D183" t="s">
+        <v>70</v>
+      </c>
+      <c r="E183" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>183</v>
+      </c>
+      <c r="B184" t="s">
+        <v>273</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D184" t="s">
+        <v>42</v>
+      </c>
+      <c r="E184" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>184</v>
+      </c>
+      <c r="B185" t="s">
+        <v>274</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D185" t="s">
+        <v>28</v>
+      </c>
+      <c r="E185" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>185</v>
+      </c>
+      <c r="B186" t="s">
+        <v>275</v>
+      </c>
+      <c r="C186" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D186" t="s">
+        <v>276</v>
+      </c>
+      <c r="E186" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <v>186</v>
+      </c>
+      <c r="B187" t="s">
+        <v>277</v>
+      </c>
+      <c r="C187" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D187" t="s">
+        <v>254</v>
+      </c>
+      <c r="E187" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <v>187</v>
+      </c>
+      <c r="B188" t="s">
+        <v>278</v>
+      </c>
+      <c r="C188" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D188" t="s">
+        <v>104</v>
+      </c>
+      <c r="E188" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A189">
+        <v>188</v>
+      </c>
+      <c r="B189" t="s">
+        <v>279</v>
+      </c>
+      <c r="C189" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D189" t="s">
+        <v>209</v>
+      </c>
+      <c r="E189" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A190">
+        <v>189</v>
+      </c>
+      <c r="B190" t="s">
+        <v>280</v>
+      </c>
+      <c r="C190" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D190" t="s">
+        <v>281</v>
+      </c>
+      <c r="E190" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>190</v>
+      </c>
+      <c r="B191" t="s">
+        <v>282</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D191" t="s">
+        <v>135</v>
+      </c>
+      <c r="E191" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A192">
+        <v>191</v>
+      </c>
+      <c r="B192" t="s">
+        <v>283</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D192" t="s">
+        <v>149</v>
+      </c>
+      <c r="E192" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A193">
+        <v>192</v>
+      </c>
+      <c r="B193" t="s">
+        <v>284</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D193" t="s">
+        <v>135</v>
+      </c>
+      <c r="E193" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A194">
+        <v>193</v>
+      </c>
+      <c r="B194" t="s">
+        <v>285</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D194" t="s">
+        <v>68</v>
+      </c>
+      <c r="E194" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A195">
+        <v>194</v>
+      </c>
+      <c r="B195" t="s">
+        <v>286</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D195" t="s">
+        <v>212</v>
+      </c>
+      <c r="E195" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A196">
+        <v>195</v>
+      </c>
+      <c r="B196" t="s">
+        <v>287</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D196" t="s">
+        <v>281</v>
+      </c>
+      <c r="E196" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A197">
+        <v>196</v>
+      </c>
+      <c r="B197" t="s">
+        <v>288</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D197" t="s">
+        <v>93</v>
+      </c>
+      <c r="E197" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A198">
+        <v>197</v>
+      </c>
+      <c r="B198" t="s">
+        <v>289</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D198" t="s">
+        <v>64</v>
+      </c>
+      <c r="E198" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A199">
+        <v>198</v>
+      </c>
+      <c r="B199" t="s">
+        <v>290</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D199" t="s">
+        <v>34</v>
+      </c>
+      <c r="E199" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A200">
+        <v>199</v>
+      </c>
+      <c r="B200" t="s">
+        <v>291</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D200" t="s">
+        <v>20</v>
+      </c>
+      <c r="E200" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A201">
+        <v>200</v>
+      </c>
+      <c r="B201" t="s">
+        <v>292</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D201" t="s">
+        <v>249</v>
+      </c>
+      <c r="E201" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A202">
+        <v>201</v>
+      </c>
+      <c r="B202" t="s">
+        <v>293</v>
+      </c>
+      <c r="C202" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D202" t="s">
+        <v>119</v>
+      </c>
+      <c r="E202" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A203">
+        <v>202</v>
+      </c>
+      <c r="B203" t="s">
+        <v>295</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D203" t="s">
+        <v>174</v>
+      </c>
+      <c r="E203" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A204">
+        <v>203</v>
+      </c>
+      <c r="B204" t="s">
+        <v>296</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D204" t="s">
+        <v>104</v>
+      </c>
+      <c r="E204" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A205">
+        <v>204</v>
+      </c>
+      <c r="B205" t="s">
+        <v>297</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D205" t="s">
+        <v>107</v>
+      </c>
+      <c r="E205" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A206">
+        <v>205</v>
+      </c>
+      <c r="B206" t="s">
+        <v>298</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D206" t="s">
+        <v>212</v>
+      </c>
+      <c r="E206" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A207">
+        <v>206</v>
+      </c>
+      <c r="B207" t="s">
+        <v>299</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D207" t="s">
+        <v>192</v>
+      </c>
+      <c r="E207" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A208">
+        <v>207</v>
+      </c>
+      <c r="B208" t="s">
+        <v>300</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D208" t="s">
+        <v>86</v>
+      </c>
+      <c r="E208" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A209">
+        <v>208</v>
+      </c>
+      <c r="B209" t="s">
+        <v>301</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D209" t="s">
+        <v>39</v>
+      </c>
+      <c r="E209" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <v>209</v>
+      </c>
+      <c r="B210" t="s">
+        <v>302</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D210" t="s">
+        <v>303</v>
+      </c>
+      <c r="E210" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <v>210</v>
+      </c>
+      <c r="B211" t="s">
+        <v>304</v>
+      </c>
+      <c r="C211" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D211" t="s">
+        <v>174</v>
+      </c>
+      <c r="E211" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A212">
+        <v>211</v>
+      </c>
+      <c r="B212" t="s">
+        <v>305</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D212" t="s">
+        <v>46</v>
+      </c>
+      <c r="E212" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>212</v>
+      </c>
+      <c r="B213" t="s">
+        <v>306</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D213" t="s">
+        <v>39</v>
+      </c>
+      <c r="E213" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A214">
+        <v>213</v>
+      </c>
+      <c r="B214" t="s">
+        <v>307</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D214" t="s">
+        <v>72</v>
+      </c>
+      <c r="E214" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <v>214</v>
+      </c>
+      <c r="B215" t="s">
+        <v>308</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D215" t="s">
+        <v>50</v>
+      </c>
+      <c r="E215" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <v>215</v>
+      </c>
+      <c r="B216" t="s">
+        <v>309</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D216" t="s">
+        <v>44</v>
+      </c>
+      <c r="E216" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A217">
+        <v>216</v>
+      </c>
+      <c r="B217" t="s">
+        <v>310</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D217" t="s">
+        <v>114</v>
+      </c>
+      <c r="E217" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A218">
+        <v>217</v>
+      </c>
+      <c r="B218" t="s">
+        <v>311</v>
+      </c>
+      <c r="C218" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D218" t="s">
+        <v>26</v>
+      </c>
+      <c r="E218" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A219">
+        <v>218</v>
+      </c>
+      <c r="B219" t="s">
+        <v>312</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D219" t="s">
+        <v>37</v>
+      </c>
+      <c r="E219" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A220">
+        <v>219</v>
+      </c>
+      <c r="B220" t="s">
+        <v>313</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D220" t="s">
+        <v>30</v>
+      </c>
+      <c r="E220" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A221">
+        <v>220</v>
+      </c>
+      <c r="B221" t="s">
+        <v>314</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D221" t="s">
+        <v>176</v>
+      </c>
+      <c r="E221" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A222">
+        <v>221</v>
+      </c>
+      <c r="B222" t="s">
+        <v>315</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D222" t="s">
+        <v>119</v>
+      </c>
+      <c r="E222" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A223">
+        <v>222</v>
+      </c>
+      <c r="B223" t="s">
+        <v>316</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D223" t="s">
+        <v>114</v>
+      </c>
+      <c r="E223" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A224">
+        <v>223</v>
+      </c>
+      <c r="B224" t="s">
+        <v>317</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D224" t="s">
+        <v>135</v>
+      </c>
+      <c r="E224" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A225">
+        <v>224</v>
+      </c>
+      <c r="B225" t="s">
+        <v>318</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D225" t="s">
+        <v>124</v>
+      </c>
+      <c r="E225" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A226">
+        <v>225</v>
+      </c>
+      <c r="B226" t="s">
+        <v>319</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D226" t="s">
+        <v>254</v>
+      </c>
+      <c r="E226" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A227">
+        <v>226</v>
+      </c>
+      <c r="B227" t="s">
+        <v>320</v>
+      </c>
+      <c r="C227" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D227" t="s">
+        <v>176</v>
+      </c>
+      <c r="E227" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A228">
+        <v>227</v>
+      </c>
+      <c r="B228" t="s">
+        <v>321</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D228" t="s">
+        <v>52</v>
+      </c>
+      <c r="E228" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A229">
+        <v>228</v>
+      </c>
+      <c r="B229" t="s">
+        <v>322</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D229" t="s">
+        <v>56</v>
+      </c>
+      <c r="E229" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A230">
+        <v>229</v>
+      </c>
+      <c r="B230" t="s">
+        <v>323</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D230" t="s">
+        <v>168</v>
+      </c>
+      <c r="E230" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A231">
+        <v>230</v>
+      </c>
+      <c r="B231" t="s">
+        <v>324</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D231" t="s">
+        <v>114</v>
+      </c>
+      <c r="E231" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A232">
+        <v>231</v>
+      </c>
+      <c r="B232" t="s">
+        <v>325</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D232" t="s">
+        <v>30</v>
+      </c>
+      <c r="E232" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A233">
+        <v>232</v>
+      </c>
+      <c r="B233" t="s">
+        <v>326</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D233" t="s">
+        <v>176</v>
+      </c>
+      <c r="E233" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A234">
+        <v>233</v>
+      </c>
+      <c r="B234" t="s">
+        <v>327</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D234" t="s">
+        <v>122</v>
+      </c>
+      <c r="E234" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A235">
+        <v>234</v>
+      </c>
+      <c r="B235" t="s">
+        <v>328</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D235" t="s">
+        <v>329</v>
+      </c>
+      <c r="E235" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A236">
+        <v>235</v>
+      </c>
+      <c r="B236" t="s">
+        <v>330</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D236" t="s">
+        <v>170</v>
+      </c>
+      <c r="E236" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A237">
+        <v>236</v>
+      </c>
+      <c r="B237" t="s">
+        <v>331</v>
+      </c>
+      <c r="C237" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D237" t="s">
+        <v>81</v>
+      </c>
+      <c r="E237" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A238">
+        <v>237</v>
+      </c>
+      <c r="B238" t="s">
+        <v>332</v>
+      </c>
+      <c r="C238" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D238" t="s">
+        <v>56</v>
+      </c>
+      <c r="E238" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A239">
+        <v>238</v>
+      </c>
+      <c r="B239" t="s">
+        <v>333</v>
+      </c>
+      <c r="C239" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D239" t="s">
+        <v>74</v>
+      </c>
+      <c r="E239" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A240">
+        <v>239</v>
+      </c>
+      <c r="B240" t="s">
+        <v>334</v>
+      </c>
+      <c r="C240" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D240" t="s">
+        <v>168</v>
+      </c>
+      <c r="E240" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A241">
+        <v>240</v>
+      </c>
+      <c r="B241" t="s">
+        <v>335</v>
+      </c>
+      <c r="C241" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D241" t="s">
+        <v>149</v>
+      </c>
+      <c r="E241" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A242">
+        <v>241</v>
+      </c>
+      <c r="B242" t="s">
+        <v>336</v>
+      </c>
+      <c r="C242" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D242" t="s">
+        <v>244</v>
+      </c>
+      <c r="E242" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A243">
+        <v>242</v>
+      </c>
+      <c r="B243" t="s">
+        <v>338</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D243" t="s">
+        <v>281</v>
+      </c>
+      <c r="E243" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A244">
+        <v>243</v>
+      </c>
+      <c r="B244" t="s">
+        <v>339</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D244" t="s">
+        <v>68</v>
+      </c>
+      <c r="E244" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A245">
+        <v>244</v>
+      </c>
+      <c r="B245" t="s">
+        <v>340</v>
+      </c>
+      <c r="C245" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D245" t="s">
+        <v>22</v>
+      </c>
+      <c r="E245" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A246">
+        <v>245</v>
+      </c>
+      <c r="B246" t="s">
+        <v>341</v>
+      </c>
+      <c r="C246" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D246" t="s">
+        <v>93</v>
+      </c>
+      <c r="E246" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A247">
+        <v>246</v>
+      </c>
+      <c r="B247" t="s">
+        <v>342</v>
+      </c>
+      <c r="C247" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D247" t="s">
+        <v>303</v>
+      </c>
+      <c r="E247" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A248">
+        <v>247</v>
+      </c>
+      <c r="B248" t="s">
+        <v>343</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D248" t="s">
+        <v>20</v>
+      </c>
+      <c r="E248" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A249">
+        <v>248</v>
+      </c>
+      <c r="B249" t="s">
+        <v>344</v>
+      </c>
+      <c r="C249" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D249" t="s">
+        <v>70</v>
+      </c>
+      <c r="E249" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A250">
+        <v>249</v>
+      </c>
+      <c r="B250" t="s">
+        <v>345</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D250" t="s">
+        <v>93</v>
+      </c>
+      <c r="E250" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A251">
+        <v>250</v>
+      </c>
+      <c r="B251" t="s">
+        <v>346</v>
+      </c>
+      <c r="C251" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D251" t="s">
+        <v>70</v>
+      </c>
+      <c r="E251" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A252">
+        <v>251</v>
+      </c>
+      <c r="B252" t="s">
+        <v>347</v>
+      </c>
+      <c r="C252" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D252" t="s">
+        <v>348</v>
+      </c>
+      <c r="E252" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A253">
+        <v>252</v>
+      </c>
+      <c r="B253" t="s">
+        <v>349</v>
+      </c>
+      <c r="C253" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D253" t="s">
+        <v>28</v>
+      </c>
+      <c r="E253" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A254">
+        <v>253</v>
+      </c>
+      <c r="B254" t="s">
+        <v>350</v>
+      </c>
+      <c r="C254" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D254" t="s">
+        <v>56</v>
+      </c>
+      <c r="E254" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A255">
+        <v>254</v>
+      </c>
+      <c r="B255" t="s">
+        <v>351</v>
+      </c>
+      <c r="C255" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D255" t="s">
+        <v>235</v>
+      </c>
+      <c r="E255" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A256">
+        <v>255</v>
+      </c>
+      <c r="B256" t="s">
+        <v>352</v>
+      </c>
+      <c r="C256" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D256" t="s">
+        <v>353</v>
+      </c>
+      <c r="E256" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A257">
+        <v>256</v>
+      </c>
+      <c r="B257" t="s">
+        <v>354</v>
+      </c>
+      <c r="C257" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D257" t="s">
+        <v>81</v>
+      </c>
+      <c r="E257" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A258">
+        <v>257</v>
+      </c>
+      <c r="B258" t="s">
+        <v>355</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D258" t="s">
+        <v>281</v>
+      </c>
+      <c r="E258" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A259">
+        <v>258</v>
+      </c>
+      <c r="B259" t="s">
+        <v>356</v>
+      </c>
+      <c r="C259" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D259" t="s">
+        <v>329</v>
+      </c>
+      <c r="E259" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A260">
+        <v>259</v>
+      </c>
+      <c r="B260" t="s">
+        <v>357</v>
+      </c>
+      <c r="C260" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D260" t="s">
+        <v>281</v>
+      </c>
+      <c r="E260" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A261">
+        <v>260</v>
+      </c>
+      <c r="B261" t="s">
+        <v>358</v>
+      </c>
+      <c r="C261" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D261" t="s">
+        <v>107</v>
+      </c>
+      <c r="E261" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A262">
+        <v>261</v>
+      </c>
+      <c r="B262" t="s">
+        <v>359</v>
+      </c>
+      <c r="C262" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D262" t="s">
+        <v>281</v>
+      </c>
+      <c r="E262" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A263">
+        <v>262</v>
+      </c>
+      <c r="B263" t="s">
+        <v>360</v>
+      </c>
+      <c r="C263" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D263" t="s">
+        <v>93</v>
+      </c>
+      <c r="E263" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A264">
+        <v>263</v>
+      </c>
+      <c r="B264" t="s">
+        <v>361</v>
+      </c>
+      <c r="C264" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D264" t="s">
+        <v>362</v>
+      </c>
+      <c r="E264" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A265">
+        <v>264</v>
+      </c>
+      <c r="B265" t="s">
+        <v>363</v>
+      </c>
+      <c r="C265" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D265" t="s">
+        <v>96</v>
+      </c>
+      <c r="E265" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A266">
+        <v>265</v>
+      </c>
+      <c r="B266" t="s">
+        <v>364</v>
+      </c>
+      <c r="C266" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D266" t="s">
+        <v>276</v>
+      </c>
+      <c r="E266" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A267">
+        <v>266</v>
+      </c>
+      <c r="B267" t="s">
+        <v>365</v>
+      </c>
+      <c r="C267" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D267" t="s">
+        <v>281</v>
+      </c>
+      <c r="E267" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A268">
+        <v>267</v>
+      </c>
+      <c r="B268" t="s">
+        <v>366</v>
+      </c>
+      <c r="C268" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D268" t="s">
+        <v>26</v>
+      </c>
+      <c r="E268" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A269">
+        <v>268</v>
+      </c>
+      <c r="B269" t="s">
+        <v>367</v>
+      </c>
+      <c r="C269" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D269" t="s">
+        <v>159</v>
+      </c>
+      <c r="E269" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A270">
+        <v>269</v>
+      </c>
+      <c r="B270" t="s">
+        <v>368</v>
+      </c>
+      <c r="C270" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D270" t="s">
+        <v>46</v>
+      </c>
+      <c r="E270" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A271">
+        <v>270</v>
+      </c>
+      <c r="B271" t="s">
+        <v>369</v>
+      </c>
+      <c r="C271" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D271" t="s">
+        <v>249</v>
+      </c>
+      <c r="E271" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A272">
+        <v>271</v>
+      </c>
+      <c r="B272" t="s">
+        <v>370</v>
+      </c>
+      <c r="C272" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D272" t="s">
+        <v>70</v>
+      </c>
+      <c r="E272" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A273">
+        <v>272</v>
+      </c>
+      <c r="B273" t="s">
+        <v>371</v>
+      </c>
+      <c r="C273" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D273" t="s">
+        <v>196</v>
+      </c>
+      <c r="E273" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A274">
+        <v>273</v>
+      </c>
+      <c r="B274" t="s">
+        <v>372</v>
+      </c>
+      <c r="C274" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D274" t="s">
+        <v>37</v>
+      </c>
+      <c r="E274" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A275">
+        <v>274</v>
+      </c>
+      <c r="B275" t="s">
+        <v>373</v>
+      </c>
+      <c r="C275" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D275" t="s">
+        <v>86</v>
+      </c>
+      <c r="E275" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A276">
+        <v>275</v>
+      </c>
+      <c r="B276" t="s">
+        <v>374</v>
+      </c>
+      <c r="C276" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D276" t="s">
+        <v>362</v>
+      </c>
+      <c r="E276" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A277">
+        <v>276</v>
+      </c>
+      <c r="B277" t="s">
+        <v>375</v>
+      </c>
+      <c r="C277" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D277" t="s">
+        <v>163</v>
+      </c>
+      <c r="E277" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A278">
+        <v>277</v>
+      </c>
+      <c r="B278" t="s">
+        <v>376</v>
+      </c>
+      <c r="C278" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D278" t="s">
+        <v>235</v>
+      </c>
+      <c r="E278" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A279">
+        <v>278</v>
+      </c>
+      <c r="B279" t="s">
+        <v>377</v>
+      </c>
+      <c r="C279" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D279" t="s">
+        <v>44</v>
+      </c>
+      <c r="E279" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A280">
+        <v>279</v>
+      </c>
+      <c r="B280" t="s">
+        <v>378</v>
+      </c>
+      <c r="C280" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D280" t="s">
+        <v>52</v>
+      </c>
+      <c r="E280" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A281">
+        <v>280</v>
+      </c>
+      <c r="B281" t="s">
+        <v>379</v>
+      </c>
+      <c r="C281" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D281" t="s">
+        <v>174</v>
+      </c>
+      <c r="E281" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A282">
+        <v>281</v>
+      </c>
+      <c r="B282" t="s">
+        <v>380</v>
+      </c>
+      <c r="C282" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D282" t="s">
+        <v>209</v>
+      </c>
+      <c r="E282" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A283">
+        <v>282</v>
+      </c>
+      <c r="B283" t="s">
+        <v>382</v>
+      </c>
+      <c r="C283" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D283" t="s">
+        <v>30</v>
+      </c>
+      <c r="E283" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A284">
+        <v>283</v>
+      </c>
+      <c r="B284" t="s">
+        <v>383</v>
+      </c>
+      <c r="C284" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D284" t="s">
+        <v>46</v>
+      </c>
+      <c r="E284" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A285">
+        <v>284</v>
+      </c>
+      <c r="B285" t="s">
+        <v>384</v>
+      </c>
+      <c r="C285" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D285" t="s">
+        <v>22</v>
+      </c>
+      <c r="E285" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A286">
+        <v>285</v>
+      </c>
+      <c r="B286" t="s">
+        <v>385</v>
+      </c>
+      <c r="C286" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D286" t="s">
+        <v>37</v>
+      </c>
+      <c r="E286" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A287">
+        <v>286</v>
+      </c>
+      <c r="B287" t="s">
+        <v>386</v>
+      </c>
+      <c r="C287" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D287" t="s">
+        <v>196</v>
+      </c>
+      <c r="E287" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A288">
+        <v>287</v>
+      </c>
+      <c r="B288" t="s">
+        <v>387</v>
+      </c>
+      <c r="C288" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D288" t="s">
+        <v>59</v>
+      </c>
+      <c r="E288" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A289">
+        <v>288</v>
+      </c>
+      <c r="B289" t="s">
+        <v>388</v>
+      </c>
+      <c r="C289" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D289" t="s">
+        <v>46</v>
+      </c>
+      <c r="E289" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A290">
+        <v>289</v>
+      </c>
+      <c r="B290" t="s">
+        <v>389</v>
+      </c>
+      <c r="C290" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D290" t="s">
+        <v>174</v>
+      </c>
+      <c r="E290" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A291">
+        <v>290</v>
+      </c>
+      <c r="B291" t="s">
+        <v>390</v>
+      </c>
+      <c r="C291" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D291" t="s">
+        <v>179</v>
+      </c>
+      <c r="E291" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A292">
+        <v>291</v>
+      </c>
+      <c r="B292" t="s">
+        <v>391</v>
+      </c>
+      <c r="C292" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D292" t="s">
+        <v>74</v>
+      </c>
+      <c r="E292" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A293">
+        <v>292</v>
+      </c>
+      <c r="B293" t="s">
+        <v>392</v>
+      </c>
+      <c r="C293" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D293" t="s">
+        <v>235</v>
+      </c>
+      <c r="E293" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A294">
+        <v>293</v>
+      </c>
+      <c r="B294" t="s">
+        <v>393</v>
+      </c>
+      <c r="C294" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D294" t="s">
+        <v>59</v>
+      </c>
+      <c r="E294" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A295">
+        <v>294</v>
+      </c>
+      <c r="B295" t="s">
+        <v>394</v>
+      </c>
+      <c r="C295" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D295" t="s">
+        <v>56</v>
+      </c>
+      <c r="E295" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A296">
+        <v>295</v>
+      </c>
+      <c r="B296" t="s">
+        <v>395</v>
+      </c>
+      <c r="C296" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D296" t="s">
+        <v>42</v>
+      </c>
+      <c r="E296" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A297">
+        <v>296</v>
+      </c>
+      <c r="B297" t="s">
+        <v>396</v>
+      </c>
+      <c r="C297" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D297" t="s">
+        <v>46</v>
+      </c>
+      <c r="E297" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A298">
+        <v>297</v>
+      </c>
+      <c r="B298" t="s">
+        <v>397</v>
+      </c>
+      <c r="C298" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D298" t="s">
+        <v>104</v>
+      </c>
+      <c r="E298" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A299">
+        <v>298</v>
+      </c>
+      <c r="B299" t="s">
+        <v>398</v>
+      </c>
+      <c r="C299" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D299" t="s">
+        <v>96</v>
+      </c>
+      <c r="E299" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A300">
+        <v>299</v>
+      </c>
+      <c r="B300" t="s">
+        <v>399</v>
+      </c>
+      <c r="C300" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D300" t="s">
+        <v>135</v>
+      </c>
+      <c r="E300" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A301">
+        <v>300</v>
+      </c>
+      <c r="B301" t="s">
+        <v>400</v>
+      </c>
+      <c r="C301" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D301" t="s">
+        <v>50</v>
+      </c>
+      <c r="E301" t="s">
         <v>8</v>
       </c>
     </row>
@@ -664,79 +6825,79 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>401</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>402</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>403</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>404</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>405</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>406</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>407</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>408</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>409</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>410</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>411</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>412</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>413</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>414</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>415</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>416</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -744,18 +6905,18 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>417</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>418</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>419</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>420</v>
       </c>
     </row>
   </sheetData>
